--- a/docs/product/essay-learning/educator-review-v1/round-1/reviewer-B/review-workbook.xlsx
+++ b/docs/product/essay-learning/educator-review-v1/round-1/reviewer-B/review-workbook.xlsx
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
